--- a/outputs/Mukaさん_QA・要望管理_2026-07-02.xlsx
+++ b/outputs/Mukaさん_QA・要望管理_2026-07-02.xlsx
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>フリーズ検知を30秒→20秒に短縮し定数化(fec1e55)</t>
+          <t>フリーズ検知を30秒→20秒に短縮し定数化(fec1e55)。タイマー進行中は誤検知しないよう調整(d1523eb)。実機で20秒超の回答待ち→誤表示なしを確認</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr"/>

--- a/outputs/Mukaさん_QA・要望管理_2026-07-02.xlsx
+++ b/outputs/Mukaさん_QA・要望管理_2026-07-02.xlsx
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>認証切れを検知したら自動でログイン画面へ移動し「セッションの有効期限が切れました。ログインし直してください。」を表示(fc7d0bf)</t>
+          <t>認証切れを検知したら自動でログイン画面へ移動し「セッションの有効期限が切れました。ログインし直してください。」を表示(fc7d0bf/12a5162)。実機で誘導動作を確認</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>No139と同対応。スタート押下時の認証切れも自動でログイン画面へ誘導(fc7d0bf)</t>
+          <t>No139と同対応。スタート押下時の認証切れも自動でログイン画面へ誘導(fc7d0bf/12a5162)</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr"/>
